--- a/public/templates/hurdexpress-orders-template.xlsx
+++ b/public/templates/hurdexpress-orders-template.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="orders" sheetId="1" r:id="rId1"/>
+    <sheet name="Захиалга" sheetId="1" r:id="rId1"/>
+    <sheet name="Заавар" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,66 +398,237 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>receiverName</v>
+        <v>Утас (заавал)</v>
       </c>
       <c r="B1" t="str">
-        <v>receiverPhone</v>
+        <v>Дүүрэг (заавал)</v>
       </c>
       <c r="C1" t="str">
-        <v>receiverAddress</v>
+        <v>Хаягийн дэлгэрэнгүй (заавал)</v>
       </c>
       <c r="D1" t="str">
-        <v>productSku</v>
+        <v>Барааны нэр (заавал)</v>
       </c>
       <c r="E1" t="str">
-        <v>qty</v>
+        <v>Тоо ширхэг (заавал)</v>
       </c>
       <c r="F1" t="str">
-        <v>codAmount</v>
+        <v>Хөнгөлөх дүн</v>
       </c>
       <c r="G1" t="str">
-        <v>note</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Бат</v>
-      </c>
-      <c r="B2" t="str">
-        <v>99112233</v>
-      </c>
-      <c r="C2" t="str">
-        <v>СБД, 1-р хороо, 12-р байр</v>
-      </c>
-      <c r="D2" t="str">
-        <v>SEED-HURD-FASHION-1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>30000</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Жишээ мөр</v>
+        <v>Тэмдэглэл</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G28"/>
+  <cols>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ЗААВАР — энэ хуудсыг импорт УНШИХГҮЙ</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>1. "Захиалга" хуудас руу шилжинэ үү.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2. 2-р мөрнөөс эхлэн захиалгаа бичнэ (1-р мөр буюу толгойг битгий устгаарай).</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>3. Хадгалаад .xlsx файлаа системд оруулна.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Жишээ:</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Утас (заавал)</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Дүүрэг (заавал)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Хаягийн дэлгэрэнгүй (заавал)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Барааны нэр (заавал)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Тоо ширхэг (заавал)</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Хөнгөлөх дүн</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Тэмдэглэл</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>99112233</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Баянзүрх</v>
+      </c>
+      <c r="C9" t="str">
+        <v>12-р хороо, 45-р байр, 12 тоот, 3 давхар</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Торон дотоож</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Оройн цагаар</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>88998877</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Хан-Уул</v>
+      </c>
+      <c r="C10" t="str">
+        <v>5-р хороо, Гоёо хотхон, B корпус 21 тоот</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Аяны аяга</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2000</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Анхаар:</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>· Барааны нэр системд бүртгэлтэй нэртэй ЯГ ТААРАХ ёстой ("Миний бараа" хэсгээс хараарай).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>· Барааны үнийг бичих ШААРДЛАГАГҮЙ — систем бараанаас нь автоматаар авна.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>· Хүлээн авагчийн нэр хэрэггүй — утасны дугаараар таних болсон.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>· Хүргэлтийн үнийг систем гэрээний дагуу өөрөө нэмнэ.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>· Хөнгөлөх дүн байхгүй бол 0 эсвэл хоосон орхино.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Дүүргийн зөв бичлэг:</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Багануур</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Багахангай</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Баянгол</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Баянзүрх</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Налайх</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Сонгинохайрхан</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Сүхбаатар</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Хан-Уул</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Чингэлтэй</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
   </ignoredErrors>
 </worksheet>
 </file>